--- a/data/k-props/2026-08-03.xlsx
+++ b/data/k-props/2026-08-03.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="76">
   <si>
     <t>date</t>
   </si>
@@ -145,103 +145,100 @@
     <t>2026-08-03</t>
   </si>
   <si>
+    <t>Andrew Alvarez</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Aaron Nola</t>
+  </si>
+  <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Brandon Sproat</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Justin Wrobleski</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Shane Bieber</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Cristian Javier</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Ian Seymour</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Michael Lorenzen</t>
+  </si>
+  <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Arizona Diamondbacks</t>
+  </si>
+  <si>
     <t>Brandon Pfaadt</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>posted</t>
-  </si>
-  <si>
-    <t>Andrew Alvarez</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Aaron Nola</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Brandon Sproat</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Justin Wrobleski</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Shane Bieber</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Cristian Javier</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Ian Seymour</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Michael Lorenzen</t>
-  </si>
-  <si>
-    <t>Michael King</t>
   </si>
 </sst>
 </file>
@@ -766,47 +763,32 @@
       <c r="B2" t="s">
         <v>44</v>
       </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-      <c r="D2">
-        <v>-215</v>
-      </c>
-      <c r="E2">
-        <v>160</v>
-      </c>
       <c r="F2">
-        <v>3.17</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>4.69</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
       </c>
-      <c r="I2">
-        <v>-0.33</v>
-      </c>
       <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2">
+        <v>4.53</v>
+      </c>
+      <c r="L2" t="s">
         <v>46</v>
       </c>
-      <c r="K2">
-        <v>3.36</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>47</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2">
+        <v>823431</v>
+      </c>
+      <c r="O2" t="s">
         <v>48</v>
       </c>
-      <c r="N2">
-        <v>825095</v>
-      </c>
-      <c r="O2" t="s">
-        <v>49</v>
-      </c>
       <c r="P2">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -815,79 +797,67 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1562</v>
+        <v>0.2196</v>
       </c>
       <c r="U2">
-        <v>0.1374</v>
+        <v>0.1953</v>
       </c>
       <c r="V2">
         <v>5</v>
       </c>
       <c r="W2">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="X2">
-        <v>0.1066</v>
+        <v>0.1518</v>
       </c>
       <c r="Y2">
-        <v>0.379</v>
+        <v>0.359</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>4.23</v>
+        <v>4.27</v>
       </c>
       <c r="AB2">
-        <v>0.9786</v>
+        <v>1.1083</v>
       </c>
       <c r="AC2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.2076</v>
+        <v>0.2351</v>
       </c>
       <c r="AE2">
-        <v>0.2108</v>
+        <v>0.2409</v>
       </c>
       <c r="AF2">
         <v>9</v>
       </c>
       <c r="AG2">
-        <v>0.2229</v>
+        <v>0.2369</v>
       </c>
       <c r="AH2">
         <v>0.2121</v>
       </c>
       <c r="AI2">
-        <v>1.0287</v>
+        <v>1.0345</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>-0.19</v>
-      </c>
-      <c r="AN2">
-        <v>-0.36</v>
-      </c>
-      <c r="AO2">
-        <v>0.36</v>
-      </c>
-      <c r="AP2">
-        <v>-0.17</v>
-      </c>
-      <c r="AQ2">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -895,34 +865,34 @@
         <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F3">
-        <v>4.78</v>
+        <v>3.82</v>
       </c>
       <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3">
+        <v>3.66</v>
+      </c>
+      <c r="L3" t="s">
         <v>46</v>
       </c>
-      <c r="J3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3">
-        <v>4.97</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>53</v>
       </c>
       <c r="N3">
         <v>823431</v>
       </c>
       <c r="O3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P3">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -934,64 +904,64 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0.2283</v>
+        <v>0.2371</v>
       </c>
       <c r="U3">
-        <v>0.2164</v>
+        <v>0.2333</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="X3">
-        <v>0.1944</v>
+        <v>0.2269</v>
       </c>
       <c r="Y3">
-        <v>0.351</v>
+        <v>0.373</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="AB3">
-        <v>1.1083</v>
+        <v>0.6779</v>
       </c>
       <c r="AC3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.2351</v>
+        <v>0.1438</v>
       </c>
       <c r="AE3">
-        <v>0.2409</v>
+        <v>0.175</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.2381</v>
+        <v>0.2059</v>
       </c>
       <c r="AH3">
         <v>0.2121</v>
       </c>
       <c r="AI3">
-        <v>1.0294</v>
+        <v>1.0205</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM3">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -999,34 +969,34 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>3.42</v>
+        <v>4.72</v>
       </c>
       <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4">
+        <v>4.56</v>
+      </c>
+      <c r="L4" t="s">
         <v>46</v>
-      </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4">
-        <v>3.61</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
       </c>
       <c r="M4" t="s">
         <v>53</v>
       </c>
       <c r="N4">
-        <v>823431</v>
+        <v>823520</v>
       </c>
       <c r="O4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1038,64 +1008,64 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0.2318</v>
+        <v>0.1657</v>
       </c>
       <c r="U4">
-        <v>0.2314</v>
+        <v>0.1671</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="X4">
-        <v>0.2308</v>
+        <v>0.1696</v>
       </c>
       <c r="Y4">
-        <v>0.369</v>
+        <v>0.359</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.35</v>
+        <v>4.07</v>
       </c>
       <c r="AB4">
-        <v>0.6779</v>
+        <v>1.1974</v>
       </c>
       <c r="AC4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD4">
-        <v>0.1438</v>
+        <v>0.254</v>
       </c>
       <c r="AE4">
-        <v>0.175</v>
+        <v>0.2507</v>
       </c>
       <c r="AF4">
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.2041</v>
+        <v>0.2439</v>
       </c>
       <c r="AH4">
         <v>0.2121</v>
       </c>
       <c r="AI4">
-        <v>1.0133</v>
+        <v>1.0207</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1103,34 +1073,34 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5">
+        <v>7.65</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5">
+        <v>7.65</v>
+      </c>
+      <c r="L5" t="s">
         <v>55</v>
       </c>
-      <c r="F5">
-        <v>4.5</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5">
-        <v>4.69</v>
-      </c>
-      <c r="L5" t="s">
-        <v>47</v>
-      </c>
       <c r="M5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N5">
         <v>823520</v>
       </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1142,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0.1663</v>
+        <v>0.3143</v>
       </c>
       <c r="U5">
-        <v>0.175</v>
+        <v>0.348</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1154,7 +1124,7 @@
         <v>110</v>
       </c>
       <c r="X5">
-        <v>0.1909</v>
+        <v>0.4091</v>
       </c>
       <c r="Y5">
         <v>0.355</v>
@@ -1163,43 +1133,43 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AB5">
-        <v>1.1974</v>
+        <v>1.0075</v>
       </c>
       <c r="AC5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.254</v>
+        <v>0.2137</v>
       </c>
       <c r="AE5">
-        <v>0.2507</v>
+        <v>0.202</v>
       </c>
       <c r="AF5">
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2426</v>
+        <v>0.2126</v>
       </c>
       <c r="AH5">
         <v>0.2121</v>
       </c>
       <c r="AI5">
-        <v>1.0109</v>
+        <v>0.9428</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM5">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
@@ -1207,34 +1177,34 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6">
+        <v>4.64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>4.48</v>
+      </c>
+      <c r="L6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" t="s">
         <v>57</v>
       </c>
-      <c r="F6">
-        <v>7.15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6">
-        <v>7.15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
       <c r="N6">
-        <v>823520</v>
+        <v>823757</v>
       </c>
       <c r="O6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1246,64 +1216,64 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0.3081</v>
+        <v>0.2028</v>
       </c>
       <c r="U6">
-        <v>0.3247</v>
+        <v>0.2096</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="X6">
-        <v>0.354</v>
+        <v>0.2222</v>
       </c>
       <c r="Y6">
-        <v>0.361</v>
+        <v>0.351</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.97</v>
+        <v>4.37</v>
       </c>
       <c r="AB6">
-        <v>1.0075</v>
+        <v>0.9697</v>
       </c>
       <c r="AC6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD6">
-        <v>0.2137</v>
+        <v>0.2057</v>
       </c>
       <c r="AE6">
-        <v>0.202</v>
+        <v>0.2125</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.2136</v>
+        <v>0.2141</v>
       </c>
       <c r="AH6">
         <v>0.2121</v>
       </c>
       <c r="AI6">
-        <v>0.9458</v>
+        <v>1.0014</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1311,34 +1281,34 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7">
+        <v>6.17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7">
+        <v>6.17</v>
+      </c>
+      <c r="L7" t="s">
         <v>59</v>
       </c>
-      <c r="F7">
-        <v>3.89</v>
-      </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7">
-        <v>4.08</v>
-      </c>
-      <c r="L7" t="s">
-        <v>47</v>
-      </c>
       <c r="M7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N7">
         <v>823757</v>
       </c>
       <c r="O7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1350,64 +1320,64 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0.2012</v>
+        <v>0.2415</v>
       </c>
       <c r="U7">
-        <v>0.1924</v>
+        <v>0.2292</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="X7">
-        <v>0.1759</v>
+        <v>0.2041</v>
       </c>
       <c r="Y7">
-        <v>0.351</v>
+        <v>0.329</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="AB7">
-        <v>0.9697</v>
+        <v>1.2448</v>
       </c>
       <c r="AC7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD7">
-        <v>0.2057</v>
+        <v>0.264</v>
       </c>
       <c r="AE7">
-        <v>0.2125</v>
+        <v>0.2429</v>
       </c>
       <c r="AF7">
         <v>9</v>
       </c>
       <c r="AG7">
-        <v>0.2115</v>
+        <v>0.2359</v>
       </c>
       <c r="AH7">
         <v>0.2121</v>
       </c>
       <c r="AI7">
-        <v>0.99</v>
+        <v>1.0756</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM7">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1415,34 +1385,34 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <v>5.45</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8">
+        <v>5.29</v>
+      </c>
+      <c r="L8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" t="s">
         <v>61</v>
       </c>
-      <c r="F8">
-        <v>5.94</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8">
-        <v>6.09</v>
-      </c>
-      <c r="L8" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" t="s">
-        <v>60</v>
-      </c>
       <c r="N8">
-        <v>823757</v>
+        <v>824647</v>
       </c>
       <c r="O8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P8">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1454,64 +1424,64 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0.2415</v>
+        <v>0.1911</v>
       </c>
       <c r="U8">
-        <v>0.2292</v>
+        <v>0.2125</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="X8">
-        <v>0.2041</v>
+        <v>0.2479</v>
       </c>
       <c r="Y8">
-        <v>0.329</v>
+        <v>0.377</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.33</v>
+        <v>4.09</v>
       </c>
       <c r="AB8">
-        <v>1.2448</v>
+        <v>1.1299</v>
       </c>
       <c r="AC8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD8">
-        <v>0.264</v>
+        <v>0.2396</v>
       </c>
       <c r="AE8">
-        <v>0.2429</v>
+        <v>0.2148</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>0.2362</v>
+        <v>0.2163</v>
       </c>
       <c r="AH8">
         <v>0.2121</v>
       </c>
       <c r="AI8">
-        <v>1.061</v>
+        <v>0.88</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM8">
-        <v>-0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1519,34 +1489,34 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>5.39</v>
+        <v>3.61</v>
       </c>
       <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>3.45</v>
+      </c>
+      <c r="L9" t="s">
         <v>46</v>
       </c>
-      <c r="J9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9">
-        <v>5.58</v>
-      </c>
-      <c r="L9" t="s">
-        <v>47</v>
-      </c>
       <c r="M9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <v>824647</v>
       </c>
       <c r="O9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P9">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1558,64 +1528,64 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>0.1928</v>
+        <v>0.2006</v>
       </c>
       <c r="U9">
-        <v>0.2217</v>
+        <v>0.1775</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="X9">
-        <v>0.2969</v>
+        <v>0.1429</v>
       </c>
       <c r="Y9">
-        <v>0.39</v>
+        <v>0.399</v>
       </c>
       <c r="Z9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="AB9">
-        <v>1.1299</v>
+        <v>0.8577</v>
       </c>
       <c r="AC9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD9">
-        <v>0.2396</v>
+        <v>0.1819</v>
       </c>
       <c r="AE9">
-        <v>0.2148</v>
+        <v>0.1875</v>
       </c>
       <c r="AF9">
         <v>9</v>
       </c>
       <c r="AG9">
-        <v>0.2197</v>
+        <v>0.1984</v>
       </c>
       <c r="AH9">
         <v>0.2121</v>
       </c>
       <c r="AI9">
-        <v>0.88</v>
+        <v>0.9639</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM9">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1623,34 +1593,34 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10">
-        <v>3.31</v>
+        <v>6.71</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10">
-        <v>3.5</v>
+        <v>6.71</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M10" t="s">
         <v>64</v>
       </c>
       <c r="N10">
-        <v>824647</v>
+        <v>822867</v>
       </c>
       <c r="O10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P10">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1662,64 +1632,64 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0.2086</v>
+        <v>0.1914</v>
       </c>
       <c r="U10">
-        <v>0.1818</v>
+        <v>0.188</v>
       </c>
       <c r="V10">
         <v>5</v>
       </c>
       <c r="W10">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="X10">
-        <v>0.1418</v>
+        <v>0.1825</v>
       </c>
       <c r="Y10">
-        <v>0.401</v>
+        <v>0.387</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="AB10">
-        <v>0.8577</v>
+        <v>1.2828</v>
       </c>
       <c r="AC10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD10">
-        <v>0.1819</v>
+        <v>0.2721</v>
       </c>
       <c r="AE10">
-        <v>0.1875</v>
+        <v>0.2496</v>
       </c>
       <c r="AF10">
         <v>9</v>
       </c>
       <c r="AG10">
-        <v>0.1985</v>
+        <v>0.2197</v>
       </c>
       <c r="AH10">
         <v>0.2121</v>
       </c>
       <c r="AI10">
-        <v>0.9669</v>
+        <v>1.0861</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM10">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
@@ -1727,34 +1697,34 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>6.62</v>
+        <v>2.99</v>
       </c>
       <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11">
+        <v>2.83</v>
+      </c>
+      <c r="L11" t="s">
         <v>46</v>
       </c>
-      <c r="J11" t="s">
-        <v>46</v>
-      </c>
-      <c r="K11">
-        <v>6.77</v>
-      </c>
-      <c r="L11" t="s">
-        <v>62</v>
-      </c>
       <c r="M11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N11">
         <v>822867</v>
       </c>
       <c r="O11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P11">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1766,64 +1736,64 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0.198</v>
+        <v>0.1558</v>
       </c>
       <c r="U11">
-        <v>0.1909</v>
+        <v>0.1554</v>
       </c>
       <c r="V11">
         <v>5</v>
       </c>
       <c r="W11">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="X11">
-        <v>0.1797</v>
+        <v>0.1545</v>
       </c>
       <c r="Y11">
-        <v>0.39</v>
+        <v>0.355</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="AB11">
-        <v>1.2828</v>
+        <v>0.9313</v>
       </c>
       <c r="AC11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD11">
-        <v>0.2721</v>
+        <v>0.1975</v>
       </c>
       <c r="AE11">
-        <v>0.2496</v>
+        <v>0.1941</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11">
-        <v>0.2207</v>
+        <v>0.2019</v>
       </c>
       <c r="AH11">
         <v>0.2121</v>
       </c>
       <c r="AI11">
-        <v>1.084</v>
+        <v>1.0068</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM11">
-        <v>-0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1831,34 +1801,34 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F12">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12">
+        <v>3.14</v>
+      </c>
+      <c r="L12" t="s">
         <v>46</v>
-      </c>
-      <c r="J12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12">
-        <v>2.88</v>
-      </c>
-      <c r="L12" t="s">
-        <v>47</v>
       </c>
       <c r="M12" t="s">
         <v>67</v>
       </c>
       <c r="N12">
-        <v>822867</v>
+        <v>824160</v>
       </c>
       <c r="O12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1870,64 +1840,64 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0.1575</v>
+        <v>0.1641</v>
       </c>
       <c r="U12">
-        <v>0.1565</v>
+        <v>0.1677</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="X12">
-        <v>0.1545</v>
+        <v>0.1743</v>
       </c>
       <c r="Y12">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.22</v>
+        <v>4.57</v>
       </c>
       <c r="AB12">
-        <v>0.9313</v>
+        <v>0.9021</v>
       </c>
       <c r="AC12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD12">
-        <v>0.1975</v>
+        <v>0.1913</v>
       </c>
       <c r="AE12">
-        <v>0.1941</v>
+        <v>0.1874</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG12">
-        <v>0.2016</v>
+        <v>0.2164</v>
       </c>
       <c r="AH12">
         <v>0.2121</v>
       </c>
       <c r="AI12">
-        <v>1.013</v>
+        <v>0.9576</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM12">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -1935,34 +1905,34 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F13">
-        <v>2.94</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13">
+        <v>1.54</v>
+      </c>
+      <c r="L13" t="s">
         <v>46</v>
       </c>
-      <c r="J13" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13">
-        <v>3.13</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N13">
         <v>824160</v>
       </c>
       <c r="O13" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="P13">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -1974,64 +1944,64 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0.1657</v>
+        <v>0.1678</v>
       </c>
       <c r="U13">
-        <v>0.1709</v>
+        <v>0.1531</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="X13">
-        <v>0.181</v>
+        <v>0.1209</v>
       </c>
       <c r="Y13">
-        <v>0.344</v>
+        <v>0.313</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.57</v>
+        <v>4.61</v>
       </c>
       <c r="AB13">
-        <v>0.9021</v>
+        <v>0.5903</v>
       </c>
       <c r="AC13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD13">
-        <v>0.1913</v>
+        <v>0.1252</v>
       </c>
       <c r="AE13">
-        <v>0.1874</v>
+        <v>0.1472</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>0.218</v>
+        <v>0.1888</v>
       </c>
       <c r="AH13">
         <v>0.2121</v>
       </c>
       <c r="AI13">
-        <v>0.962</v>
+        <v>0.948</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM13">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -2039,34 +2009,34 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14">
+        <v>6.22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14">
+        <v>6.22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" t="s">
         <v>71</v>
       </c>
-      <c r="F14">
-        <v>1.34</v>
-      </c>
-      <c r="H14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14">
-        <v>1.53</v>
-      </c>
-      <c r="L14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M14" t="s">
-        <v>70</v>
-      </c>
       <c r="N14">
-        <v>824160</v>
+        <v>824324</v>
       </c>
       <c r="O14" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="P14">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -2078,64 +2048,64 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>0.184</v>
+        <v>0.2842</v>
       </c>
       <c r="U14">
-        <v>0.1625</v>
+        <v>0.3031</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="X14">
-        <v>0.1136</v>
+        <v>0.3398</v>
       </c>
       <c r="Y14">
-        <v>0.306</v>
+        <v>0.34</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>4.57</v>
+        <v>4.13</v>
       </c>
       <c r="AB14">
-        <v>0.5903</v>
+        <v>1.0303</v>
       </c>
       <c r="AC14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD14">
-        <v>0.1252</v>
+        <v>0.2185</v>
       </c>
       <c r="AE14">
-        <v>0.1472</v>
+        <v>0.2232</v>
       </c>
       <c r="AF14">
         <v>9</v>
       </c>
       <c r="AG14">
-        <v>0.1866</v>
+        <v>0.2504</v>
       </c>
       <c r="AH14">
         <v>0.2121</v>
       </c>
       <c r="AI14">
-        <v>0.9541</v>
+        <v>1.067</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM14">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2143,34 +2113,34 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15">
-        <v>5.98</v>
+        <v>2.83</v>
       </c>
       <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15">
+        <v>2.67</v>
+      </c>
+      <c r="L15" t="s">
         <v>46</v>
       </c>
-      <c r="J15" t="s">
-        <v>46</v>
-      </c>
-      <c r="K15">
-        <v>6.13</v>
-      </c>
-      <c r="L15" t="s">
-        <v>62</v>
-      </c>
       <c r="M15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N15">
         <v>824324</v>
       </c>
       <c r="O15" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="P15">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2182,64 +2152,64 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0.2845</v>
+        <v>0.1492</v>
       </c>
       <c r="U15">
-        <v>0.3086</v>
+        <v>0.1286</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X15">
-        <v>0.3564</v>
+        <v>0.0882</v>
       </c>
       <c r="Y15">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>4.13</v>
+        <v>4.8</v>
       </c>
       <c r="AB15">
-        <v>1.0303</v>
+        <v>1.0626</v>
       </c>
       <c r="AC15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD15">
-        <v>0.2185</v>
+        <v>0.2254</v>
       </c>
       <c r="AE15">
-        <v>0.2232</v>
+        <v>0.2222</v>
       </c>
       <c r="AF15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG15">
-        <v>0.2531</v>
+        <v>0.1929</v>
       </c>
       <c r="AH15">
         <v>0.2121</v>
       </c>
       <c r="AI15">
-        <v>1.0783</v>
+        <v>0.88</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM15">
-        <v>-0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2247,34 +2217,34 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F16">
-        <v>2.79</v>
+        <v>5.23</v>
       </c>
       <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16">
+        <v>5.07</v>
+      </c>
+      <c r="L16" t="s">
         <v>46</v>
-      </c>
-      <c r="J16" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16">
-        <v>2.98</v>
-      </c>
-      <c r="L16" t="s">
-        <v>47</v>
       </c>
       <c r="M16" t="s">
         <v>74</v>
       </c>
       <c r="N16">
-        <v>824324</v>
+        <v>825095</v>
       </c>
       <c r="O16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P16">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2286,64 +2256,64 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>0.1538</v>
+        <v>0.2147</v>
       </c>
       <c r="U16">
-        <v>0.143</v>
+        <v>0.2245</v>
       </c>
       <c r="V16">
         <v>5</v>
       </c>
       <c r="W16">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="X16">
-        <v>0.1226</v>
+        <v>0.2414</v>
       </c>
       <c r="Y16">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AB16">
-        <v>1.0626</v>
+        <v>1.0288</v>
       </c>
       <c r="AC16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD16">
-        <v>0.2254</v>
+        <v>0.2182</v>
       </c>
       <c r="AE16">
-        <v>0.2222</v>
+        <v>0.207</v>
       </c>
       <c r="AF16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG16">
-        <v>0.1938</v>
+        <v>0.2003</v>
       </c>
       <c r="AH16">
         <v>0.2121</v>
       </c>
       <c r="AI16">
-        <v>0.88</v>
+        <v>0.9426</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2351,34 +2321,43 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="C17">
+        <v>3.5</v>
+      </c>
+      <c r="D17">
+        <v>-215</v>
+      </c>
+      <c r="E17">
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>4.67</v>
+        <v>3.36</v>
       </c>
       <c r="H17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17">
+        <v>3.2</v>
+      </c>
+      <c r="L17" t="s">
         <v>46</v>
       </c>
-      <c r="J17" t="s">
-        <v>46</v>
-      </c>
-      <c r="K17">
-        <v>4.86</v>
-      </c>
-      <c r="L17" t="s">
-        <v>47</v>
-      </c>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="N17">
         <v>825095</v>
       </c>
       <c r="O17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P17">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2387,67 +2366,67 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17">
-        <v>0.2119</v>
+        <v>0.1517</v>
       </c>
       <c r="U17">
-        <v>0.215</v>
+        <v>0.1333</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="X17">
-        <v>0.2203</v>
+        <v>0.104</v>
       </c>
       <c r="Y17">
-        <v>0.371</v>
+        <v>0.385</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
       <c r="AB17">
-        <v>1.0288</v>
+        <v>0.9786</v>
       </c>
       <c r="AC17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AD17">
-        <v>0.2182</v>
+        <v>0.2076</v>
       </c>
       <c r="AE17">
-        <v>0.207</v>
+        <v>0.2108</v>
       </c>
       <c r="AF17">
         <v>9</v>
       </c>
       <c r="AG17">
-        <v>0.2021</v>
+        <v>0.2198</v>
       </c>
       <c r="AH17">
         <v>0.2121</v>
       </c>
       <c r="AI17">
-        <v>0.9386</v>
+        <v>1.0097</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM17">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
